--- a/00 - Docs/00 - FC_Docs/ACwing_FC_A_CPL.xlsx
+++ b/00 - Docs/00 - FC_Docs/ACwing_FC_A_CPL.xlsx
@@ -494,12 +494,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>21.8000mm</t>
+          <t>24.8000mm</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>27.8000mm</t>
+          <t>24.8000mm</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -544,12 +544,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>8.7196mm</t>
+          <t>4.0709mm</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14.1567mm</t>
+          <t>10.2816mm</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6">
@@ -594,12 +594,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>19.0000mm</t>
+          <t>15.4000mm</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12.7000mm</t>
+          <t>14.2000mm</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -619,12 +619,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17.0000mm</t>
+          <t>19.5770mm</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>17.6000mm</t>
+          <t>13.2654mm</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -644,12 +644,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22.2000mm</t>
+          <t>24.6022mm</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30.2000mm</t>
+          <t>27.2509mm</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -669,12 +669,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21.6000mm</t>
+          <t>24.6000mm</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>23.4000mm</t>
+          <t>20.4000mm</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21.6000mm</t>
+          <t>24.6000mm</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22.4000mm</t>
+          <t>19.4000mm</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15.6000mm</t>
+          <t>11.6000mm</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20.6000mm</t>
+          <t>21.6000mm</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17.3000mm</t>
+          <t>13.3000mm</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14">
@@ -869,12 +869,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>23.0000mm</t>
+          <t>26.0000mm</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>23.9000mm</t>
+          <t>20.9000mm</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17.7000mm</t>
+          <t>20.7000mm</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28.6000mm</t>
+          <t>25.6000mm</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -919,12 +919,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>12.4000mm</t>
+          <t>15.4000mm</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>21.0000mm</t>
+          <t>18.0000mm</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>21.6000mm</t>
+          <t>24.6000mm</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20.4000mm</t>
+          <t>17.4000mm</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>14.5500mm</t>
+          <t>17.5500mm</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>28.4000mm</t>
+          <t>25.4000mm</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>13.4736mm</t>
+          <t>16.3500mm</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>27.0196mm</t>
+          <t>24.4000mm</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>270</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>15.7500mm</t>
+          <t>18.5202mm</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>18.4000mm</t>
+          <t>15.5928mm</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>12.0000mm</t>
+          <t>15.0000mm</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>24.8000mm</t>
+          <t>21.8000mm</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>22.0000mm</t>
+          <t>22.9959mm</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>13.4000mm</t>
+          <t>12.5644mm</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>270</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27">
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>4.6157mm</t>
+          <t>6.2749mm</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>8.5032mm</t>
+          <t>7.0015mm</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>13.0500mm</t>
+          <t>8.2000mm</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>1.4866mm</t>
+          <t>18.1000mm</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>8.8281mm</t>
+          <t>11.0000mm</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>3.7663mm</t>
+          <t>17.2000mm</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="39">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>90</v>
+        <v>270</v>
       </c>
     </row>
     <row r="40">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>3.1250mm</t>
+          <t>11.8000mm</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>16.6000mm</t>
+          <t>36.8500mm</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>270</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>11.5146mm</t>
+          <t>14.5146mm</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>22.3109mm</t>
+          <t>19.3109mm</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>12.2500mm</t>
+          <t>15.2500mm</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>23.6866mm</t>
+          <t>20.6866mm</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>4.7019mm</t>
+          <t>3.1000mm</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>4.6511mm</t>
+          <t>15.4000mm</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>21.0000mm</t>
+          <t>13.6000mm</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22.0000mm</t>
+          <t>13.9964mm</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>11.4000mm</t>
+          <t>9.9496mm</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="55">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>23.8000mm</t>
+          <t>26.8000mm</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>29.6000mm</t>
+          <t>26.6000mm</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -1819,12 +1819,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23.8000mm</t>
+          <t>26.0000mm</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>30.6000mm</t>
+          <t>27.6000mm</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>11.4000mm</t>
+          <t>14.4000mm</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>17.8000mm</t>
+          <t>14.8000mm</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>11.4000mm</t>
+          <t>14.4000mm</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>16.8000mm</t>
+          <t>13.8000mm</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21.6000mm</t>
+          <t>24.6000mm</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>21.4000mm</t>
+          <t>18.4000mm</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>25.6000mm</t>
+          <t>28.6500mm</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>22.6000mm</t>
+          <t>19.6866mm</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>25.6000mm</t>
+          <t>28.6500mm</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>23.6000mm</t>
+          <t>20.6866mm</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>22.0000mm</t>
+          <t>22.6000mm</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>18.0000mm</t>
+          <t>14.0000mm</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>23.0000mm</t>
+          <t>23.6000mm</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>18.0000mm</t>
+          <t>14.0000mm</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>23.4000mm</t>
+          <t>26.4000mm</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>25.6000mm</t>
+          <t>22.6000mm</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -2094,12 +2094,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>23.9832mm</t>
+          <t>26.9832mm</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>24.0524mm</t>
+          <t>21.0524mm</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23.4000mm</t>
+          <t>26.4000mm</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>26.6000mm</t>
+          <t>23.6000mm</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23.4000mm</t>
+          <t>26.4000mm</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>27.6000mm</t>
+          <t>24.6000mm</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10.6063mm</t>
+          <t>13.6063mm</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>24.3003mm</t>
+          <t>21.3003mm</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -2194,12 +2194,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>19.1000mm</t>
+          <t>14.6000mm</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>28.6000mm</t>
+          <t>28.0000mm</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>18.1250mm</t>
+          <t>14.6000mm</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>29.9929mm</t>
+          <t>29.0000mm</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>10.9500mm</t>
+          <t>13.5391mm</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>20.5134mm</t>
+          <t>27.0002mm</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2269,12 +2269,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>19.8000mm</t>
+          <t>16.2000mm</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>30.0000mm</t>
+          <t>29.2000mm</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>180</v>
+        <v>270</v>
       </c>
     </row>
     <row r="75">
@@ -2319,12 +2319,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>22.0000mm</t>
+          <t>21.6281mm</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>15.0000mm</t>
+          <t>15.1472mm</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>180</v>
+        <v>270</v>
       </c>
     </row>
     <row r="77">
@@ -2344,12 +2344,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>17.4243mm</t>
+          <t>17.6000mm</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>15.6263mm</t>
+          <t>12.2000mm</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>180</v>
+        <v>270</v>
       </c>
     </row>
     <row r="78">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18.8000mm</t>
+          <t>17.5514mm</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>13.6000mm</t>
+          <t>14.2333mm</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>12.9213mm</t>
+          <t>10.4000mm</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>7.2671mm</t>
+          <t>14.0000mm</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="83">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>14.1621mm</t>
+          <t>11.4000mm</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>6.3212mm</t>
+          <t>14.0000mm</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="84">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>16.4000mm</t>
+          <t>12.4000mm</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="85">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>17.0000mm</t>
+          <t>20.0000mm</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>23.0000mm</t>
+          <t>20.0000mm</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>19.0000mm</t>
+          <t>15.4000mm</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>11.0000mm</t>
+          <t>12.2000mm</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>16.0000mm</t>
+          <t>19.0000mm</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>29.0745mm</t>
+          <t>26.0745mm</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>26.8687mm</t>
+          <t>28.9319mm</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>16.3973mm</t>
+          <t>16.4271mm</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11.2645mm</t>
+          <t>7.9000mm</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>4.8243mm</t>
+          <t>15.0000mm</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>11.4000mm</t>
+          <t>14.4000mm</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>25.4000mm</t>
+          <t>22.4000mm</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">

--- a/00 - Docs/00 - FC_Docs/ACwing_FC_A_CPL.xlsx
+++ b/00 - Docs/00 - FC_Docs/ACwing_FC_A_CPL.xlsx
@@ -1439,42 +1439,42 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>26.0000mm</t>
+          <t>35.7670mm</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>33.0000mm</t>
+          <t>4.2330mm</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>270</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>35.7670mm</t>
+          <t>21.5000mm</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>4.2330mm</t>
+          <t>3.1250mm</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1483,23 +1483,23 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21.5000mm</t>
+          <t>36.9000mm</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>3.1250mm</t>
+          <t>23.6000mm</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -1508,13 +1508,13 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>J4</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>23.6000mm</t>
+          <t>15.7000mm</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -1539,17 +1539,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>J4</t>
+          <t>J5</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>36.9000mm</t>
+          <t>22.0000mm</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>15.7000mm</t>
+          <t>36.8500mm</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -1558,18 +1558,18 @@
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>J5</t>
+          <t>J6</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22.0000mm</t>
+          <t>11.8000mm</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1589,22 +1589,22 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>J6</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>11.8000mm</t>
+          <t>14.5146mm</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>36.8500mm</t>
+          <t>19.3109mm</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="E47" s="2" t="n">
@@ -1614,17 +1614,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14.5146mm</t>
+          <t>15.2500mm</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>19.3109mm</t>
+          <t>20.6866mm</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -1633,28 +1633,28 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>15.2500mm</t>
+          <t>3.1000mm</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>20.6866mm</t>
+          <t>15.4000mm</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="E49" s="2" t="n">
@@ -1664,17 +1664,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>3.1000mm</t>
+          <t>26.6000mm</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>15.4000mm</t>
+          <t>15.6000mm</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -1683,23 +1683,23 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26.6000mm</t>
+          <t>29.0000mm</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>15.6000mm</t>
+          <t>14.4000mm</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -1708,23 +1708,23 @@
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>29.0000mm</t>
+          <t>13.6000mm</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>14.4000mm</t>
+          <t>11.4000mm</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -1739,17 +1739,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>13.6000mm</t>
+          <t>13.9964mm</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>11.4000mm</t>
+          <t>9.9496mm</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -1758,48 +1758,48 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>13.9964mm</t>
+          <t>26.8000mm</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>9.9496mm</t>
+          <t>26.6000mm</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>26.8000mm</t>
+          <t>26.0000mm</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>26.6000mm</t>
+          <t>27.6000mm</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -1814,17 +1814,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>26.0000mm</t>
+          <t>14.4000mm</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>27.6000mm</t>
+          <t>14.8000mm</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>14.8000mm</t>
+          <t>13.8000mm</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -1864,17 +1864,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>14.4000mm</t>
+          <t>30.6000mm</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>13.8000mm</t>
+          <t>5.4000mm</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -1889,17 +1889,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>30.6000mm</t>
+          <t>34.6000mm</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>5.4000mm</t>
+          <t>9.4000mm</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -1908,23 +1908,23 @@
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R14</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>34.6000mm</t>
+          <t>24.6000mm</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>9.4000mm</t>
+          <t>18.4000mm</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -1933,23 +1933,23 @@
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>24.6000mm</t>
+          <t>28.6500mm</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>18.4000mm</t>
+          <t>19.6866mm</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>19.6866mm</t>
+          <t>20.6866mm</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -1989,17 +1989,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R17</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>28.6500mm</t>
+          <t>22.6000mm</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>20.6866mm</t>
+          <t>14.0000mm</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2008,18 +2008,18 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>R17</t>
+          <t>R18</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>22.6000mm</t>
+          <t>23.6000mm</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2039,17 +2039,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>R18</t>
+          <t>R20</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>23.6000mm</t>
+          <t>26.4000mm</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>14.0000mm</t>
+          <t>22.6000mm</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -2058,23 +2058,23 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>R20</t>
+          <t>R21</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>26.4000mm</t>
+          <t>26.9832mm</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>22.6000mm</t>
+          <t>21.0524mm</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -2083,23 +2083,23 @@
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>R21</t>
+          <t>R22</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>26.9832mm</t>
+          <t>26.4000mm</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>21.0524mm</t>
+          <t>23.6000mm</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -2108,13 +2108,13 @@
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>R22</t>
+          <t>R23</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>23.6000mm</t>
+          <t>24.6000mm</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -2139,17 +2139,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>R23</t>
+          <t>R24</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>26.4000mm</t>
+          <t>13.6063mm</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>24.6000mm</t>
+          <t>21.3003mm</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -2158,23 +2158,23 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>R24</t>
+          <t>R25</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>13.6063mm</t>
+          <t>14.6000mm</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>21.3003mm</t>
+          <t>28.0000mm</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>R25</t>
+          <t>R26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>28.0000mm</t>
+          <t>29.0000mm</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -2214,17 +2214,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>R26</t>
+          <t>R27</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>14.6000mm</t>
+          <t>13.5391mm</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>29.0000mm</t>
+          <t>27.0002mm</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -2239,17 +2239,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>R27</t>
+          <t>R28</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13.5391mm</t>
+          <t>16.2000mm</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>27.0002mm</t>
+          <t>29.2000mm</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -2258,73 +2258,73 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>R28</t>
+          <t>R34</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>16.2000mm</t>
+          <t>3.0500mm</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>29.2000mm</t>
+          <t>35.5300mm</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>270</v>
+        <v>90</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>R34</t>
+          <t>R37</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>3.0500mm</t>
+          <t>21.6281mm</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>35.5300mm</t>
+          <t>15.1472mm</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>90</v>
+        <v>270</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>R37</t>
+          <t>R38</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>21.6281mm</t>
+          <t>17.6000mm</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>15.1472mm</t>
+          <t>12.2000mm</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -2339,17 +2339,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>R38</t>
+          <t>R39</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>17.6000mm</t>
+          <t>17.5514mm</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>12.2000mm</t>
+          <t>14.2333mm</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -2364,17 +2364,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>R39</t>
+          <t>R40</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>17.5514mm</t>
+          <t>34.0000mm</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>14.2333mm</t>
+          <t>26.6000mm</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -2389,17 +2389,17 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>R40</t>
+          <t>R41</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>34.0000mm</t>
+          <t>33.0500mm</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>26.6000mm</t>
+          <t>26.5134mm</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -2414,17 +2414,17 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>R41</t>
+          <t>R42</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>33.0500mm</t>
+          <t>20.6000mm</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>26.5134mm</t>
+          <t>2.8000mm</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -2433,43 +2433,43 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>R42</t>
+          <t>R47</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>20.6000mm</t>
+          <t>10.4000mm</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>2.8000mm</t>
+          <t>14.0000mm</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>R47</t>
+          <t>R48</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10.4000mm</t>
+          <t>11.4000mm</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -2489,22 +2489,22 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>R48</t>
+          <t>R49</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>11.4000mm</t>
+          <t>26.0000mm</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>14.0000mm</t>
+          <t>33.0000mm</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">

--- a/00 - Docs/00 - FC_Docs/ACwing_FC_A_CPL.xlsx
+++ b/00 - Docs/00 - FC_Docs/ACwing_FC_A_CPL.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.56" customWidth="1" min="1" max="1"/>
@@ -1314,67 +1314,67 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>C50</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>9.0000mm</t>
+          <t>13.6700mm</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>1.6000mm</t>
+          <t>4.1500mm</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>180</v>
+        <v>270</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
+          <t>9.0000mm</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
           <t>1.6000mm</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>9.0000mm</t>
-        </is>
-      </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>270</v>
+        <v>180</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>31.0000mm</t>
+          <t>1.6000mm</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>38.4000mm</t>
+          <t>9.0000mm</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1383,48 +1383,48 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>180</v>
+        <v>270</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
+          <t>31.0000mm</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
           <t>38.4000mm</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>31.0000mm</t>
-        </is>
-      </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>270</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25.2032mm</t>
+          <t>38.4000mm</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>12.7499mm</t>
+          <t>31.0000mm</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1433,23 +1433,23 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>35.7670mm</t>
+          <t>25.2032mm</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>4.2330mm</t>
+          <t>12.7499mm</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1458,23 +1458,23 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21.5000mm</t>
+          <t>35.7670mm</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>3.1250mm</t>
+          <t>4.2330mm</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1483,23 +1483,23 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>36.9000mm</t>
+          <t>21.5000mm</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>23.6000mm</t>
+          <t>3.1250mm</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -1508,13 +1508,13 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>J4</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>15.7000mm</t>
+          <t>23.6000mm</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -1539,17 +1539,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>J5</t>
+          <t>J4</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>22.0000mm</t>
+          <t>36.9000mm</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>36.8500mm</t>
+          <t>15.7000mm</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -1558,18 +1558,18 @@
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>J6</t>
+          <t>J5</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>11.8000mm</t>
+          <t>22.0000mm</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1589,22 +1589,22 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>J6</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>14.5146mm</t>
+          <t>11.8000mm</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>19.3109mm</t>
+          <t>36.8500mm</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="E47" s="2" t="n">
@@ -1614,17 +1614,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>15.2500mm</t>
+          <t>14.5146mm</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>20.6866mm</t>
+          <t>19.3109mm</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -1633,28 +1633,28 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>3.1000mm</t>
+          <t>15.2500mm</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>15.4000mm</t>
+          <t>20.6866mm</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="E49" s="2" t="n">
@@ -1664,17 +1664,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26.6000mm</t>
+          <t>3.1000mm</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>15.6000mm</t>
+          <t>15.4000mm</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -1683,23 +1683,23 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>29.0000mm</t>
+          <t>26.6000mm</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>14.4000mm</t>
+          <t>15.6000mm</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -1708,23 +1708,23 @@
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>13.6000mm</t>
+          <t>29.0000mm</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>11.4000mm</t>
+          <t>14.4000mm</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -1739,17 +1739,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>13.9964mm</t>
+          <t>13.6000mm</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>9.9496mm</t>
+          <t>11.4000mm</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -1758,48 +1758,48 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>26.8000mm</t>
+          <t>13.9964mm</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>26.6000mm</t>
+          <t>9.9496mm</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>26.0000mm</t>
+          <t>26.8000mm</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>27.6000mm</t>
+          <t>26.6000mm</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -1814,17 +1814,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14.4000mm</t>
+          <t>26.0000mm</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>14.8000mm</t>
+          <t>27.6000mm</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>13.8000mm</t>
+          <t>14.8000mm</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -1864,17 +1864,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>30.6000mm</t>
+          <t>14.4000mm</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>5.4000mm</t>
+          <t>13.8000mm</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -1889,17 +1889,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>34.6000mm</t>
+          <t>30.6000mm</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>9.4000mm</t>
+          <t>5.4000mm</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -1908,23 +1908,23 @@
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>24.6000mm</t>
+          <t>34.6000mm</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>18.4000mm</t>
+          <t>9.4000mm</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -1933,23 +1933,23 @@
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>R14</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>28.6500mm</t>
+          <t>24.6000mm</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>19.6866mm</t>
+          <t>18.4000mm</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>20.6866mm</t>
+          <t>19.6866mm</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -1989,17 +1989,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>R17</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>22.6000mm</t>
+          <t>28.6500mm</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>14.0000mm</t>
+          <t>20.6866mm</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2008,18 +2008,18 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>R18</t>
+          <t>R17</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>23.6000mm</t>
+          <t>22.6000mm</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2039,17 +2039,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>R20</t>
+          <t>R18</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>26.4000mm</t>
+          <t>23.6000mm</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>22.6000mm</t>
+          <t>14.0000mm</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -2058,23 +2058,23 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>R21</t>
+          <t>R20</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>26.9832mm</t>
+          <t>26.4000mm</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>21.0524mm</t>
+          <t>22.6000mm</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -2083,23 +2083,23 @@
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>R22</t>
+          <t>R21</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>26.4000mm</t>
+          <t>26.9832mm</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>23.6000mm</t>
+          <t>21.0524mm</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -2108,13 +2108,13 @@
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>R23</t>
+          <t>R22</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>24.6000mm</t>
+          <t>23.6000mm</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -2139,17 +2139,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>R24</t>
+          <t>R23</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>13.6063mm</t>
+          <t>26.4000mm</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>21.3003mm</t>
+          <t>24.6000mm</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -2158,23 +2158,23 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>R25</t>
+          <t>R24</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14.6000mm</t>
+          <t>13.6063mm</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>28.0000mm</t>
+          <t>21.3003mm</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>R26</t>
+          <t>R25</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>29.0000mm</t>
+          <t>28.0000mm</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -2214,17 +2214,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>R27</t>
+          <t>R26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13.5391mm</t>
+          <t>14.6000mm</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>27.0002mm</t>
+          <t>29.0000mm</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -2239,17 +2239,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>R28</t>
+          <t>R27</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>16.2000mm</t>
+          <t>13.5391mm</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>29.2000mm</t>
+          <t>27.0002mm</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -2258,73 +2258,73 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>R34</t>
+          <t>R28</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>3.0500mm</t>
+          <t>16.2000mm</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>35.5300mm</t>
+          <t>29.2000mm</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>90</v>
+        <v>270</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>R37</t>
+          <t>R34</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>21.6281mm</t>
+          <t>3.0500mm</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>15.1472mm</t>
+          <t>35.5300mm</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>270</v>
+        <v>90</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>R38</t>
+          <t>R37</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>17.6000mm</t>
+          <t>21.6281mm</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>12.2000mm</t>
+          <t>15.1472mm</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -2339,17 +2339,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>R39</t>
+          <t>R38</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>17.5514mm</t>
+          <t>17.6000mm</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>14.2333mm</t>
+          <t>12.2000mm</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -2364,17 +2364,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>R40</t>
+          <t>R39</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>34.0000mm</t>
+          <t>11.7712mm</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>26.6000mm</t>
+          <t>2.8420mm</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -2383,23 +2383,23 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>R41</t>
+          <t>R40</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>33.0500mm</t>
+          <t>34.0000mm</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>26.5134mm</t>
+          <t>26.6000mm</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -2414,17 +2414,17 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>R42</t>
+          <t>R41</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>20.6000mm</t>
+          <t>33.0500mm</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>2.8000mm</t>
+          <t>26.5134mm</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -2433,43 +2433,43 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>R47</t>
+          <t>R42</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>10.4000mm</t>
+          <t>20.6000mm</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>14.0000mm</t>
+          <t>2.8000mm</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>R48</t>
+          <t>R47</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>11.4000mm</t>
+          <t>10.4000mm</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -2489,22 +2489,22 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>R49</t>
+          <t>R48</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>26.0000mm</t>
+          <t>11.4000mm</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>33.0000mm</t>
+          <t>14.0000mm</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
@@ -2764,25 +2764,50 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>11.5200mm</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>4.8000mm</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>14.4000mm</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>22.4000mm</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="n">
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n">
         <v>90</v>
       </c>
     </row>

--- a/00 - Docs/00 - FC_Docs/ACwing_FC_A_CPL.xlsx
+++ b/00 - Docs/00 - FC_Docs/ACwing_FC_A_CPL.xlsx
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15">
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17">
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22">
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31">
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>270</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>270</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>35.7670mm</t>
+          <t>34.7346mm</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>4.2330mm</t>
+          <t>5.2654mm</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="50">
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="56">
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="57">
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="58">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="59">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="60">
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="62">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="63">
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="64">
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="67">
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="69">
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="70">
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="72">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="73">
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="74">
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="79">
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="82">
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="92">
@@ -2733,7 +2733,7 @@
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>270</v>
+        <v>90</v>
       </c>
     </row>
     <row r="93">
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="94">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
